--- a/dsa/educosys/DSA Course Questions.xlsx
+++ b/dsa/educosys/DSA Course Questions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AnilSaiDonga\workspace\dsa\educosys\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA541855-2496-4F25-AA4C-3C847D25B20F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412CA483-4BF6-441E-9B0B-83358AB5C620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1176" yWindow="888" windowWidth="20724" windowHeight="11112" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Class Quess" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="110">
   <si>
     <t>https://leetcode.com/problems/fibonacci-number</t>
   </si>
@@ -358,7 +358,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -414,6 +414,13 @@
       <color rgb="FF1155CC"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -432,10 +439,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -449,8 +457,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -672,6 +682,7 @@
   <cols>
     <col min="1" max="1" width="81.21875" customWidth="1"/>
     <col min="2" max="2" width="43.6640625" customWidth="1"/>
+    <col min="3" max="3" width="34.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -726,11 +737,17 @@
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="B7" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="B8" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
@@ -746,9 +763,12 @@
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="B12" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="9" t="s">
         <v>11</v>
       </c>
     </row>

--- a/dsa/educosys/DSA Course Questions.xlsx
+++ b/dsa/educosys/DSA Course Questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AnilSaiDonga\workspace\dsa\educosys\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412CA483-4BF6-441E-9B0B-83358AB5C620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C3A7810-2394-43C8-9FB3-3787934249B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1176" yWindow="888" windowWidth="20724" windowHeight="11112" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Class Quess" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="110">
   <si>
     <t>https://leetcode.com/problems/fibonacci-number</t>
   </si>
@@ -758,6 +758,9 @@
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="B10" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
@@ -770,6 +773,9 @@
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">

--- a/dsa/educosys/DSA Course Questions.xlsx
+++ b/dsa/educosys/DSA Course Questions.xlsx
@@ -1,32 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AnilSaiDonga\workspace\dsa\educosys\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C3A7810-2394-43C8-9FB3-3787934249B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Class Quess" sheetId="1" r:id="rId1"/>
-    <sheet name="Homework Quess" sheetId="2" r:id="rId2"/>
-    <sheet name="More Questions for Practise" sheetId="3" r:id="rId3"/>
+    <sheet name="Class Quess" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Homework Quess" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="More Questions for Practise" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
   <si>
     <t>https://leetcode.com/problems/fibonacci-number</t>
   </si>
   <si>
+    <t>done</t>
+  </si>
+  <si>
     <t>https://leetcode.com/problems/n-th-tribonacci-number</t>
   </si>
   <si>
@@ -105,7 +104,7 @@
     <t>https://leetcode.com/problems/best-time-to-buy-and-sell-stock-iv/</t>
   </si>
   <si>
-    <t>Binary Trees</t>
+    <t xml:space="preserve">Binary Trees</t>
   </si>
   <si>
     <t>https://leetcode.com/problems/path-sum-ii</t>
@@ -174,7 +173,7 @@
     <t>https://leetcode.com/problems/unique-binary-search-trees</t>
   </si>
   <si>
-    <t>N-ary Trees</t>
+    <t xml:space="preserve">N-ary Trees</t>
   </si>
   <si>
     <t>https://leetcode.com/problems/n-ary-tree-level-order-traversal/</t>
@@ -213,7 +212,7 @@
     <t>https://leetcode.com/problems/word-ladder</t>
   </si>
   <si>
-    <t>Topological Sorting</t>
+    <t xml:space="preserve">Topological Sorting</t>
   </si>
   <si>
     <t>https://leetcode.com/problems/course-schedule</t>
@@ -222,7 +221,7 @@
     <t>https://leetcode.com/problems/course-schedule-ii</t>
   </si>
   <si>
-    <t>Dijkstra Algo / Bellman Ford Algo / Floyd Warshall Algo</t>
+    <t xml:space="preserve">Dijkstra Algo / Bellman Ford Algo / Floyd Warshall Algo</t>
   </si>
   <si>
     <t>https://practice.geeksforgeeks.org/problems/implementing-dijkstra-set-1-adjacency-matrix/1</t>
@@ -237,7 +236,7 @@
     <t>https://leetcode.com/problems/find-the-city-with-the-smallest-number-of-neighbors-at-a-threshold-distance</t>
   </si>
   <si>
-    <t>Prim's algorithm</t>
+    <t xml:space="preserve">Prim's algorithm</t>
   </si>
   <si>
     <t>https://leetcode.com/problems/min-cost-to-connect-all-points</t>
@@ -349,119 +348,98 @@
   </si>
   <si>
     <t>https://leetcode.com/problems/find-center-of-star-graph</t>
-  </si>
-  <si>
-    <t>done</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="6">
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF1155CC"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <sz val="10.000000"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="10"/>
+      <sz val="10.000000"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10.000000"/>
+      <color indexed="4"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10.000000"/>
       <color rgb="FF1155CC"/>
       <name val="Arial"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF1155CC"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="10"/>
+      <b/>
+      <sz val="10.000000"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  <cellStyleXfs count="3">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="8">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1"/>
+    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Good" xfId="2" builtinId="26"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -476,8 +454,291 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -534,7 +795,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -560,7 +821,7 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -612,16 +873,28 @@
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -637,7 +910,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -668,793 +941,805 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B96"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="81.21875" customWidth="1"/>
-    <col min="2" max="2" width="43.6640625" customWidth="1"/>
-    <col min="3" max="3" width="34.33203125" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="81.21875"/>
+    <col customWidth="1" min="2" max="2" width="43.6640625"/>
+    <col customWidth="1" min="3" max="3" width="34.33203125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>7</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="B10" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>11</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+    <row r="16">
+      <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+    <row r="17">
+      <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20">
       <c r="A20" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+    <row r="24">
+      <c r="A24" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+    <row r="25">
+      <c r="A25" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+    <row r="26">
+      <c r="A26" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32">
+      <c r="A32" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40">
       <c r="A40" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41">
       <c r="A41" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43">
       <c r="A43" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45">
       <c r="A45" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46">
       <c r="A46" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="47">
       <c r="A47" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49">
       <c r="A49" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50">
       <c r="A50" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="52">
       <c r="A52" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
+    <row r="53">
+      <c r="A53" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
+    <row r="54">
+      <c r="A54" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+    <row r="55">
+      <c r="A55" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
+    <row r="56">
+      <c r="A56" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57">
+      <c r="A57" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="59">
       <c r="A59" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B59" s="6"/>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60">
+      <c r="A60" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="62">
       <c r="A62" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63">
+      <c r="A63" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="65">
       <c r="A65" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
+    <row r="66">
+      <c r="A66" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67">
+      <c r="A67" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="68">
       <c r="A68" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="69">
       <c r="A69" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="70">
       <c r="A70" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="71">
       <c r="A71" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="72">
       <c r="A72" s="6"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="73">
       <c r="A73" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="74">
       <c r="A74" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="75">
       <c r="A75" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="76">
       <c r="A76" s="6"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="77">
       <c r="A77" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="78">
       <c r="A78" s="6"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="79">
       <c r="A79" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="80">
       <c r="A80" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="81">
       <c r="A81" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="82">
       <c r="A82" s="6"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83">
       <c r="A83" s="6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="84">
       <c r="A84" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="85">
       <c r="A85" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="86">
       <c r="A86" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="87">
       <c r="A87" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="88">
       <c r="A88" s="6"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="89">
       <c r="A89" s="6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="90">
       <c r="A90" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="91">
       <c r="A91" s="6"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="92">
       <c r="A92" s="6"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="93">
       <c r="A93" s="6"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="95">
       <c r="A95" s="6"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="96">
       <c r="A96" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="A2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="A3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="A4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="A5" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="A6" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="A7" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="A8" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="A9" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="A10" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="A12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="A13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="A15" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="A16" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="A17" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="A18" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="A20" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="A21" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="A23" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="A24" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="A25" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="A26" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="A27" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="A28" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="A29" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="A31" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="A32" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="A35" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="A36" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="A37" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="A38" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="A39" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="A40" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="A41" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="A43" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="A44" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="A45" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="A46" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="A47" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="A49" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="A50" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="A53" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="A54" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="A55" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="A56" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="A57" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="A59" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="A60" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="A63" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="A66" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="A67" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="A68" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="A69" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="A70" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="A71" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="A73" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="A74" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="A75" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="A77" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="A80" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="A81" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="A84" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="A85" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="A86" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="A87" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="A90" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink r:id="rId1" ref="A1"/>
+    <hyperlink r:id="rId2" ref="A2"/>
+    <hyperlink r:id="rId3" ref="A3"/>
+    <hyperlink r:id="rId4" ref="A4"/>
+    <hyperlink r:id="rId5" ref="A5"/>
+    <hyperlink r:id="rId6" ref="A6"/>
+    <hyperlink r:id="rId7" ref="A7"/>
+    <hyperlink r:id="rId8" ref="A8"/>
+    <hyperlink r:id="rId9" ref="A9"/>
+    <hyperlink r:id="rId10" ref="A10"/>
+    <hyperlink r:id="rId11" ref="A12"/>
+    <hyperlink r:id="rId12" ref="A13"/>
+    <hyperlink r:id="rId13" ref="A15"/>
+    <hyperlink r:id="rId14" ref="A16"/>
+    <hyperlink r:id="rId15" ref="A17"/>
+    <hyperlink r:id="rId16" ref="A18"/>
+    <hyperlink r:id="rId17" ref="A20"/>
+    <hyperlink r:id="rId18" ref="A21"/>
+    <hyperlink r:id="rId19" ref="A23"/>
+    <hyperlink r:id="rId20" ref="A24"/>
+    <hyperlink r:id="rId21" ref="A25"/>
+    <hyperlink r:id="rId22" ref="A26"/>
+    <hyperlink r:id="rId23" ref="A27"/>
+    <hyperlink r:id="rId24" ref="A28"/>
+    <hyperlink r:id="rId25" ref="A29"/>
+    <hyperlink r:id="rId26" ref="A31"/>
+    <hyperlink r:id="rId27" ref="A32"/>
+    <hyperlink r:id="rId28" ref="A35"/>
+    <hyperlink r:id="rId29" ref="A36"/>
+    <hyperlink r:id="rId30" ref="A37"/>
+    <hyperlink r:id="rId31" ref="A38"/>
+    <hyperlink r:id="rId32" ref="A39"/>
+    <hyperlink r:id="rId33" ref="A40"/>
+    <hyperlink r:id="rId34" ref="A41"/>
+    <hyperlink r:id="rId35" ref="A43"/>
+    <hyperlink r:id="rId36" ref="A44"/>
+    <hyperlink r:id="rId37" ref="A45"/>
+    <hyperlink r:id="rId38" ref="A46"/>
+    <hyperlink r:id="rId39" ref="A47"/>
+    <hyperlink r:id="rId40" ref="A49"/>
+    <hyperlink r:id="rId41" ref="A50"/>
+    <hyperlink r:id="rId42" ref="A53"/>
+    <hyperlink r:id="rId43" ref="A54"/>
+    <hyperlink r:id="rId44" ref="A55"/>
+    <hyperlink r:id="rId45" ref="A56"/>
+    <hyperlink r:id="rId46" ref="A57"/>
+    <hyperlink r:id="rId47" ref="A59"/>
+    <hyperlink r:id="rId48" ref="A60"/>
+    <hyperlink r:id="rId49" ref="A63"/>
+    <hyperlink r:id="rId50" ref="A66"/>
+    <hyperlink r:id="rId51" ref="A67"/>
+    <hyperlink r:id="rId52" ref="A68"/>
+    <hyperlink r:id="rId53" ref="A69"/>
+    <hyperlink r:id="rId54" ref="A70"/>
+    <hyperlink r:id="rId55" ref="A71"/>
+    <hyperlink r:id="rId56" ref="A73"/>
+    <hyperlink r:id="rId57" ref="A74"/>
+    <hyperlink r:id="rId58" ref="A75"/>
+    <hyperlink r:id="rId59" ref="A77"/>
+    <hyperlink r:id="rId60" ref="A80"/>
+    <hyperlink r:id="rId61" ref="A81"/>
+    <hyperlink r:id="rId62" ref="A84"/>
+    <hyperlink r:id="rId63" ref="A85"/>
+    <hyperlink r:id="rId64" ref="A86"/>
+    <hyperlink r:id="rId65" ref="A87"/>
+    <hyperlink r:id="rId66" ref="A90"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="66.88671875" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="66.88671875"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+    <row r="6">
+      <c r="A6" s="7" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+    <row r="7">
+      <c r="A7" s="7" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+    <row r="8">
+      <c r="A8" s="7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+    <row r="9">
+      <c r="A9" s="7" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+    <row r="10">
+      <c r="A10" s="7" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11">
+      <c r="A11" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" s="6"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="A2" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="A3" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
-    <hyperlink ref="A5" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
-    <hyperlink ref="A6" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
-    <hyperlink ref="A7" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
-    <hyperlink ref="A8" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
-    <hyperlink ref="A9" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
-    <hyperlink ref="A10" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
-    <hyperlink ref="A11" r:id="rId10" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
-    <hyperlink ref="A14" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
-    <hyperlink ref="A15" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
-    <hyperlink ref="A16" r:id="rId13" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
-    <hyperlink ref="A20" r:id="rId14" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
-    <hyperlink ref="A21" r:id="rId15" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
+    <hyperlink r:id="rId1" ref="A1"/>
+    <hyperlink r:id="rId2" ref="A2"/>
+    <hyperlink r:id="rId3" ref="A3"/>
+    <hyperlink r:id="rId4" ref="A5"/>
+    <hyperlink r:id="rId5" ref="A6"/>
+    <hyperlink r:id="rId6" ref="A7"/>
+    <hyperlink r:id="rId7" ref="A8"/>
+    <hyperlink r:id="rId8" ref="A9"/>
+    <hyperlink r:id="rId9" ref="A10"/>
+    <hyperlink r:id="rId10" ref="A11"/>
+    <hyperlink r:id="rId11" ref="A14"/>
+    <hyperlink r:id="rId12" ref="A15"/>
+    <hyperlink r:id="rId13" ref="A16"/>
+    <hyperlink r:id="rId14" ref="A20"/>
+    <hyperlink r:id="rId15" ref="A21"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="57.77734375" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="57.77734375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="1" ht="13.199999999999999">
+      <c r="A1" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="2" ht="13.199999999999999">
+      <c r="A2" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="3" ht="13.199999999999999">
+      <c r="A3" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" ht="13.199999999999999">
       <c r="A4" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" ht="13.199999999999999">
       <c r="A5" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="13.199999999999999">
+      <c r="A6" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" ht="13.199999999999999">
       <c r="A10" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" ht="13.199999999999999">
       <c r="A11" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" ht="13.199999999999999">
       <c r="A12" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" ht="13.199999999999999">
       <c r="A13" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" ht="13.199999999999999">
       <c r="A14" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" ht="13.199999999999999">
       <c r="A15" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" ht="13.199999999999999">
       <c r="A16" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" ht="13.199999999999999">
       <c r="A17" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" ht="13.199999999999999">
       <c r="A19" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" ht="13.199999999999999">
       <c r="A20" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" ht="13.199999999999999">
       <c r="A21" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" ht="13.199999999999999">
       <c r="A22" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" ht="13.199999999999999">
       <c r="A24" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" ht="13.199999999999999">
       <c r="A25" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
-    <hyperlink ref="A2" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
-    <hyperlink ref="A3" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
-    <hyperlink ref="A4" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
-    <hyperlink ref="A5" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
-    <hyperlink ref="A6" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000005000000}"/>
-    <hyperlink ref="A8" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
-    <hyperlink ref="A11" r:id="rId8" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
-    <hyperlink ref="A12" r:id="rId9" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
-    <hyperlink ref="A13" r:id="rId10" xr:uid="{00000000-0004-0000-0200-000009000000}"/>
-    <hyperlink ref="A14" r:id="rId11" xr:uid="{00000000-0004-0000-0200-00000A000000}"/>
-    <hyperlink ref="A15" r:id="rId12" xr:uid="{00000000-0004-0000-0200-00000B000000}"/>
-    <hyperlink ref="A16" r:id="rId13" xr:uid="{00000000-0004-0000-0200-00000C000000}"/>
-    <hyperlink ref="A17" r:id="rId14" xr:uid="{00000000-0004-0000-0200-00000D000000}"/>
-    <hyperlink ref="A19" r:id="rId15" xr:uid="{00000000-0004-0000-0200-00000E000000}"/>
-    <hyperlink ref="A20" r:id="rId16" xr:uid="{00000000-0004-0000-0200-00000F000000}"/>
-    <hyperlink ref="A21" r:id="rId17" xr:uid="{00000000-0004-0000-0200-000010000000}"/>
-    <hyperlink ref="A22" r:id="rId18" xr:uid="{00000000-0004-0000-0200-000011000000}"/>
-    <hyperlink ref="A25" r:id="rId19" xr:uid="{00000000-0004-0000-0200-000012000000}"/>
+    <hyperlink r:id="rId1" ref="A1"/>
+    <hyperlink r:id="rId2" ref="A2"/>
+    <hyperlink r:id="rId3" ref="A3"/>
+    <hyperlink r:id="rId4" ref="A4"/>
+    <hyperlink r:id="rId5" ref="A5"/>
+    <hyperlink r:id="rId6" ref="A6"/>
+    <hyperlink r:id="rId7" ref="A8"/>
+    <hyperlink r:id="rId8" ref="A11"/>
+    <hyperlink r:id="rId9" ref="A12"/>
+    <hyperlink r:id="rId10" ref="A13"/>
+    <hyperlink r:id="rId11" ref="A14"/>
+    <hyperlink r:id="rId12" ref="A15"/>
+    <hyperlink r:id="rId13" ref="A16"/>
+    <hyperlink r:id="rId14" ref="A17"/>
+    <hyperlink r:id="rId15" ref="A19"/>
+    <hyperlink r:id="rId16" ref="A20"/>
+    <hyperlink r:id="rId17" ref="A21"/>
+    <hyperlink r:id="rId18" ref="A22"/>
+    <hyperlink r:id="rId19" ref="A25"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/dsa/educosys/DSA Course Questions.xlsx
+++ b/dsa/educosys/DSA Course Questions.xlsx
@@ -18,12 +18,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
   <si>
     <t>https://leetcode.com/problems/fibonacci-number</t>
   </si>
   <si>
     <t>done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. recursion
+    time complexity: O(2^n) two times fuction call
+    space complexity: O(n) recursion stack
+2. recursion with memoization (top down) why you think you can do memoization ? because there are overlapping sub-problems
+    time complexity : O(n) because we only compute once every value and store it in dp vector
+    space complexity: O(n) + O(n) = O(n)
+                 recursion stack + dp vector
+3. iteration approach with tabulation (bottom up approach) this is to optimize space complexity
+    time complexity: O(n) for loop going from 2 to n
+    space complexity: O(1) we are not using any space except two constant variables</t>
   </si>
   <si>
     <t>https://leetcode.com/problems/n-th-tribonacci-number</t>
@@ -422,9 +434,12 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf fontId="2" fillId="2" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -954,20 +969,23 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="81.21875"/>
     <col customWidth="1" min="2" max="2" width="43.6640625"/>
-    <col customWidth="1" min="3" max="3" width="34.33203125"/>
+    <col customWidth="1" min="3" max="3" width="47.140625"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="216.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -975,7 +993,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
@@ -983,7 +1001,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
@@ -991,7 +1009,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
@@ -999,7 +1017,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
@@ -1007,7 +1025,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
@@ -1015,7 +1033,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>1</v>
@@ -1023,7 +1041,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
         <v>1</v>
@@ -1031,7 +1049,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
         <v>1</v>
@@ -1039,7 +1057,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -1047,348 +1065,348 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>13</v>
+      <c r="A15" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>14</v>
+      <c r="A16" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>15</v>
+      <c r="A17" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="s">
-        <v>16</v>
+      <c r="A18" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1"/>
     <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>17</v>
+      <c r="A20" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="s">
-        <v>18</v>
+      <c r="A21" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="s">
-        <v>19</v>
+      <c r="A23" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="s">
-        <v>20</v>
+      <c r="A24" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="s">
-        <v>21</v>
+      <c r="A25" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="s">
-        <v>22</v>
+      <c r="A26" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="s">
-        <v>23</v>
+      <c r="A27" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="s">
-        <v>24</v>
+      <c r="A28" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="s">
-        <v>25</v>
+      <c r="A29" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="s">
-        <v>26</v>
+      <c r="A31" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="s">
-        <v>27</v>
+      <c r="A32" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="s">
-        <v>28</v>
+      <c r="A34" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="s">
-        <v>29</v>
+      <c r="A35" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="s">
-        <v>30</v>
+      <c r="A36" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="s">
-        <v>31</v>
+      <c r="A37" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="s">
-        <v>32</v>
+      <c r="A38" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="s">
-        <v>33</v>
+      <c r="A39" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="s">
-        <v>34</v>
+      <c r="A40" s="3" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="s">
-        <v>35</v>
+      <c r="A41" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="s">
-        <v>36</v>
+      <c r="A43" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="s">
-        <v>37</v>
+      <c r="A44" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="s">
-        <v>38</v>
+      <c r="A45" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="s">
-        <v>39</v>
+      <c r="A46" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="s">
-        <v>40</v>
+      <c r="A47" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="s">
-        <v>41</v>
+      <c r="A49" s="3" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="s">
-        <v>42</v>
+      <c r="A50" s="3" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="s">
-        <v>43</v>
+      <c r="A52" s="6" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="s">
-        <v>44</v>
+      <c r="A53" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="s">
-        <v>45</v>
+      <c r="A54" s="3" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="s">
-        <v>46</v>
+      <c r="A55" s="3" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="s">
-        <v>47</v>
+      <c r="A56" s="3" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="s">
-        <v>48</v>
+      <c r="A57" s="3" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B59" s="6"/>
+      <c r="A59" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B59" s="7"/>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="s">
-        <v>50</v>
+      <c r="A60" s="3" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="s">
-        <v>51</v>
+      <c r="A62" s="6" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="s">
-        <v>52</v>
+      <c r="A63" s="3" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="s">
-        <v>53</v>
+      <c r="A65" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="s">
-        <v>54</v>
+      <c r="A66" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="s">
-        <v>55</v>
+      <c r="A67" s="3" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="s">
-        <v>56</v>
+      <c r="A68" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="s">
-        <v>57</v>
+      <c r="A69" s="3" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="s">
-        <v>58</v>
+      <c r="A70" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="s">
-        <v>59</v>
+      <c r="A71" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="6"/>
+      <c r="A72" s="7"/>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="s">
-        <v>60</v>
+      <c r="A73" s="3" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="s">
-        <v>61</v>
+      <c r="A74" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="s">
-        <v>62</v>
+      <c r="A75" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="6"/>
+      <c r="A76" s="7"/>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="s">
-        <v>63</v>
+      <c r="A77" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="6"/>
+      <c r="A78" s="7"/>
     </row>
     <row r="79">
-      <c r="A79" s="6" t="s">
-        <v>64</v>
+      <c r="A79" s="7" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="s">
-        <v>65</v>
+      <c r="A80" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="s">
-        <v>66</v>
+      <c r="A81" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="6"/>
+      <c r="A82" s="7"/>
     </row>
     <row r="83">
-      <c r="A83" s="6" t="s">
-        <v>67</v>
+      <c r="A83" s="7" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="s">
-        <v>68</v>
+      <c r="A84" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="s">
-        <v>69</v>
+      <c r="A85" s="3" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="s">
-        <v>70</v>
+      <c r="A86" s="3" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="s">
-        <v>71</v>
+      <c r="A87" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="6"/>
+      <c r="A88" s="7"/>
     </row>
     <row r="89">
-      <c r="A89" s="6" t="s">
-        <v>72</v>
+      <c r="A89" s="7" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="s">
-        <v>73</v>
+      <c r="A90" s="3" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="6"/>
+      <c r="A91" s="7"/>
     </row>
     <row r="92">
-      <c r="A92" s="6"/>
+      <c r="A92" s="7"/>
     </row>
     <row r="93">
-      <c r="A93" s="6"/>
+      <c r="A93" s="7"/>
     </row>
     <row r="95">
-      <c r="A95" s="6"/>
+      <c r="A95" s="7"/>
     </row>
     <row r="96">
-      <c r="A96" s="6"/>
+      <c r="A96" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1478,101 +1496,101 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>74</v>
+      <c r="A1" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>75</v>
+      <c r="A2" s="3" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>76</v>
+      <c r="A3" s="3" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>77</v>
+      <c r="A5" s="8" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="s">
-        <v>78</v>
+      <c r="A6" s="8" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
-        <v>79</v>
+      <c r="A7" s="8" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>80</v>
+      <c r="A8" s="8" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="s">
-        <v>81</v>
+      <c r="A9" s="8" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
-        <v>82</v>
+      <c r="A10" s="8" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="s">
-        <v>83</v>
+      <c r="A11" s="8" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="s">
-        <v>84</v>
+      <c r="A13" s="6" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>85</v>
+      <c r="A14" s="3" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>86</v>
+      <c r="A15" s="3" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>87</v>
+      <c r="A16" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6"/>
+      <c r="A18" s="7"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="s">
-        <v>88</v>
+      <c r="A19" s="6" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>89</v>
+      <c r="A20" s="3" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="s">
-        <v>90</v>
+      <c r="A21" s="3" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5"/>
+      <c r="A23" s="6"/>
     </row>
     <row r="24">
-      <c r="A24" s="6"/>
+      <c r="A24" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1611,108 +1629,108 @@
   </cols>
   <sheetData>
     <row r="1" ht="13.199999999999999">
-      <c r="A1" s="2" t="s">
-        <v>91</v>
+      <c r="A1" s="3" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="2" ht="13.199999999999999">
-      <c r="A2" s="2" t="s">
-        <v>92</v>
+      <c r="A2" s="3" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="3" ht="13.199999999999999">
-      <c r="A3" s="2" t="s">
-        <v>93</v>
+      <c r="A3" s="3" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="4" ht="13.199999999999999">
-      <c r="A4" s="2" t="s">
-        <v>94</v>
+      <c r="A4" s="3" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="5" ht="13.199999999999999">
-      <c r="A5" s="2" t="s">
-        <v>95</v>
+      <c r="A5" s="3" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="6" ht="13.199999999999999">
-      <c r="A6" s="2" t="s">
-        <v>96</v>
+      <c r="A6" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>97</v>
+      <c r="A8" s="3" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="10" ht="13.199999999999999">
-      <c r="A10" s="5" t="s">
-        <v>84</v>
+      <c r="A10" s="6" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="11" ht="13.199999999999999">
-      <c r="A11" s="2" t="s">
-        <v>98</v>
+      <c r="A11" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="12" ht="13.199999999999999">
-      <c r="A12" s="2" t="s">
-        <v>99</v>
+      <c r="A12" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="13" ht="13.199999999999999">
-      <c r="A13" s="2" t="s">
-        <v>100</v>
+      <c r="A13" s="3" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="14" ht="13.199999999999999">
-      <c r="A14" s="2" t="s">
-        <v>101</v>
+      <c r="A14" s="3" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="15" ht="13.199999999999999">
-      <c r="A15" s="2" t="s">
-        <v>102</v>
+      <c r="A15" s="3" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="16" ht="13.199999999999999">
-      <c r="A16" s="2" t="s">
-        <v>103</v>
+      <c r="A16" s="3" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="17" ht="13.199999999999999">
-      <c r="A17" s="2" t="s">
-        <v>104</v>
+      <c r="A17" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="19" ht="13.199999999999999">
-      <c r="A19" s="2" t="s">
-        <v>105</v>
+      <c r="A19" s="3" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="20" ht="13.199999999999999">
-      <c r="A20" s="2" t="s">
-        <v>106</v>
+      <c r="A20" s="3" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="21" ht="13.199999999999999">
-      <c r="A21" s="2" t="s">
-        <v>107</v>
+      <c r="A21" s="3" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="22" ht="13.199999999999999">
-      <c r="A22" s="2" t="s">
-        <v>108</v>
+      <c r="A22" s="3" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="24" ht="13.199999999999999">
-      <c r="A24" s="5" t="s">
-        <v>53</v>
+      <c r="A24" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="25" ht="13.199999999999999">
-      <c r="A25" s="2" t="s">
-        <v>109</v>
+      <c r="A25" s="3" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/dsa/educosys/DSA Course Questions.xlsx
+++ b/dsa/educosys/DSA Course Questions.xlsx
@@ -18,26 +18,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
   <si>
     <t>https://leetcode.com/problems/fibonacci-number</t>
   </si>
   <si>
-    <t>done</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. recursion
-    time complexity: O(2^n) two times fuction call
-    space complexity: O(n) recursion stack
-2. recursion with memoization (top down) why you think you can do memoization ? because there are overlapping sub-problems
-    time complexity : O(n) because we only compute once every value and store it in dp vector
-    space complexity: O(n) + O(n) = O(n)
-                 recursion stack + dp vector
-3. iteration approach with tabulation (bottom up approach) this is to optimize space complexity
-    time complexity: O(n) for loop going from 2 to n
-    space complexity: O(1) we are not using any space except two constant variables</t>
-  </si>
-  <si>
     <t>https://leetcode.com/problems/n-th-tribonacci-number</t>
   </si>
   <si>
@@ -56,13 +41,255 @@
     <t>https://leetcode.com/problems/generate-parentheses</t>
   </si>
   <si>
+    <t xml:space="preserve">* time complexity: O(n * Cn) where Cn = (2n)!/((n + 1)! * n!)    ( catalan number )
+* space complexity: O(n * Cn) where Cn = (2n)!/((n + 1)! * n!)    ( catalan number )
+since there are n pairs, you need to generate Cn = (2n)!/((n + 1)! * n!) valid parentheses combinations    
+if ( c == n) push curr to res and return
+if ( o &lt; n ) add '('    
+if ( o &gt; c ) add ')'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /* recursion    
+     * time complexity: O(n * c) where c = (2n)!/((n + 1)! * n!)    (Catalan number)
+     * space complexity: O(n * c) where c = (2n)!/((n + 1)! * n!)    
+     */
+    void helper(int n, int o, int c, string curr, vector&lt;string&gt;&amp; res)
+    {
+        if (curr.size() &gt;= 2*n) // or you can also tell if (c == n), since c is calculated after o
+        {
+            res.push_back(curr);
+            return;
+        }
+        if (o &lt; n)    helper(n, o + 1, c, curr + '(', res);
+        if (o &gt; c)    helper(n, o, c + 1, curr + ')', res);
+    }
+    vector&lt;string&gt; generateParenthesis(int n) {
+        vector&lt;string&gt; res;
+        helper(n, 0, 0, "", res);    
+        return res;
+    }</t>
+  </si>
+  <si>
     <t>https://leetcode.com/problems/decode-ways</t>
   </si>
   <si>
+    <t xml:space="preserve">you are given a string number like "1234", you are supposed to decode it like ABCD. you can decode it considering single digit or double digit    
+* solve through recursion    
+    time complexity: O(2^n)    
+    space complexity: O(n) (recursive call stack)    
+* solve through recursion with memoization    
+    time complexity: O(n) ( since we are calculating and storing in dp array )    
+    space complexity: O(n) + O(n) ( recursive stack + dp array )    
+* solve through tabulation with dp    
+    time complexity: O(n) (since we are calculating and storing in dp array )    
+    space complexity: O(n) ( dp array )    
+* solve through tabulation with space optimization    
+    time complexity: O(n)    
+    space complexity: O(1) ( only using variables )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /*    
+     * recursive solution    
+     * time complexity: O(2^n) (two helper function calls)    
+     * space complexity: O(n) (recursive stack)    
+     */
+    // public int helper(String s, int ind, int n)
+    // {
+    //     if (ind &gt;= n) return 1; 
+    //     int ways = 0;    
+    //     // single digit    
+    //     if (s.charAt(ind) != '0') ways += helper(s, ind + 1, n);    
+    //     // double digit    
+    //     if (ind &lt; n - 1)
+    //     if ((s.charAt(ind) == '1' || (s.charAt(ind) == '2' &amp;&amp; s.charAt(ind + 1) &lt;= '6')))     
+    //         ways += helper(s, ind + 2, n);
+    //     return ways;
+    // }
+    // public int numDecodings(String s) {    
+    //     if (s.charAt(0) == '0') return 0;    
+    //     int n = s.length();
+    //     return helper(s, 0, n);
+    // }    
+    /*    
+     * recursive solution    
+     * time complexity: O(n) ( since we are calculating and storing in dp )    
+     * space complexity: O(n) + O(n) (recursive stack)    
+     */
+    // public int helper(String s, int ind, int n, int[] dp)
+    // {
+    //     if (ind &gt;= n) return 1;    
+    //     // if dp[ind] calcualted, return it    
+    //     if (dp[ind] != -1) return dp[ind];    
+    //     int ways = 0;
+    //     // single digit    
+    //     if (s.charAt(ind) != '0') ways += helper(s, ind + 1, n, dp);    
+    //     // double digit    
+    //     if (ind &lt; n - 1)
+    //     if ((s.charAt(ind) == '1' || (s.charAt(ind) == '2' &amp;&amp; s.charAt(ind + 1) &lt;= '6')))     
+    //         ways += helper(s, ind + 2, n, dp);
+    //     return dp[ind] = ways;    
+    // }
+    // public int numDecodings(String s) {    
+    //     if (s.charAt(0) == '0') return 0;    
+    //     int n = s.length();    
+    //     int[] dp = new int[n];
+    //     for (int i = 0; i &lt; n; i++) dp[i] = -1;
+    //     return helper(s, 0, n, dp);
+    // }    
+    /*
+     * iteration    
+     * time complexity: O(n)    
+     * space complexity: O(n) (dp array)    
+     */
+    // public int numDecodings(String s) {    
+    //     if (s.charAt(0) == '0') return 0;   
+    //     int n = s.length();     
+    //     int[] dp = new int[n + 1];
+    //     // initial conditions    
+    //     dp[0] = 1;
+    //     dp[1] = 1;
+    //     for (int i = 2; i &lt;= n; i++)
+    //     {
+    //         int singleDigit = Integer.valueOf(s.substring(i - 1, i));
+    //         int doubleDigit = Integer.valueOf(s.substring(i - 2, i));
+    //         if (singleDigit &gt;= 1) dp[i] += dp[i - 1];
+    //         if (doubleDigit &gt;= 10 &amp;&amp; doubleDigit &lt;= 26) dp[i] += dp[i - 2];
+    //     }    
+    //     return dp[n];
+    // }    
+    /*
+     * iteration    
+     * time complexity: O(n)    
+     * space complexity: O(1) (only using variables)     
+     */
+    public int numDecodings(String s) {    
+        if (s.charAt(0) == '0') return 0;   
+        int n = s.length();     
+        // initial conditions    
+        int prevPrev = 1;
+        int prev = 1;
+        for (int i = 2; i &lt;= n; i++)
+        {
+            int singleDigit = Integer.valueOf(s.substring(i - 1, i));
+            int doubleDigit = Integer.valueOf(s.substring(i - 2, i));
+            int curr = 0;
+            if (singleDigit &gt;= 1) curr += prev;
+            if (doubleDigit &gt;= 10 &amp;&amp; doubleDigit &lt;= 26) curr += prevPrev;    
+            prevPrev = prev;    
+            prev = curr;    
+        }    
+        return prev;    
+    }    </t>
+  </si>
+  <si>
     <t>https://leetcode.com/problems/combinations</t>
   </si>
   <si>
+    <t xml:space="preserve">* go from 0 to n or n to 0    
+* have the base case    
+* also check ind is going out of bounds, if going out of bounds return    
+* include case and back track    
+* exclude case    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /* recursion    
+     * time complexity: O(nCk * k) (there are nCk combinations and there are k values in each combination)    where nCk = n!/((n - k)! * k!)    
+     * space complexity: O(k)    
+     */    
+    public void helper(int n, int k, int ind, List&lt;Integer&gt; curr, List&lt;List&lt;Integer&gt;&gt; res)
+    {
+        if (curr.size() == k)
+        {
+            res.add(new ArrayList&lt;&gt;(curr));
+            return;
+        }    
+        if (ind &gt; n)
+        {
+            return;    
+        }
+        // include wala case    
+        curr.add(ind);
+        helper(n, k, ind + 1, curr, res);
+        curr.remove(curr.size() - 1);
+        // exclude wala case    
+        helper(n, k, ind + 1, curr, res);    
+    }
+    public List&lt;List&lt;Integer&gt;&gt; combine(int n, int k) {
+        List&lt;List&lt;Integer&gt;&gt; res = new ArrayList&lt;&gt;();
+        List&lt;Integer&gt; curr = new ArrayList&lt;&gt;();
+        helper(n, k, 1, curr, res);
+        return res;
+    }    </t>
+  </si>
+  <si>
     <t>https://leetcode.com/problems/permutations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">two ways to solve this through recursion    
+* either solve this using and extra used boolean array    ( no index there )
+* or solve this using in place swapping with nums, keep track of ind    ( index there here )    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /* recursion    
+     * time complexity: O(n * nPn)    
+     * space complexity: O(n) + O(n) ( each permutation will have recursive depth of n  + used array )    
+     */    
+    // public void helper(int[] nums, boolean[] used, List&lt;Integer&gt; curr, List&lt;List&lt;Integer&gt;&gt; res)    
+    // {
+    //     if (curr.size() == nums.length)
+    //     {
+    //         res.add(new ArrayList&lt;&gt;(curr));
+    //         return;
+    //     }    
+    //     for (int i = 0; i &lt; nums.length; i++)    
+    //     {
+    //         if (used[i] == true) continue;
+    //         used[i] = true;    
+    //         curr.add(nums[i]);    
+    //         helper(nums, used, curr, res);    
+    //         curr.remove(curr.size() - 1);    
+    //         used[i] = false;    
+    //     }
+    // }
+    // public List&lt;List&lt;Integer&gt;&gt; permute(int[] nums) {
+    //     List&lt;List&lt;Integer&gt;&gt; res = new ArrayList&lt;&gt;();
+    //     List&lt;Integer&gt; curr = new ArrayList&lt;&gt;();    
+    //     boolean[] used = new boolean[nums.length];
+    //     Arrays.fill(used, false);
+    //     helper(nums, used, curr, res);    
+    //     return res;    
+    // }    
+    /* recursion    
+     * time complexity: O(n * nPn)    
+     * space complexity: O(n) ( each permutation will have recursive depth of n )    
+     */    
+    public void swap(int[] nums, int i, int j)
+    {
+        int temp = nums[i];    
+        nums[i] = nums[j];    
+        nums[j] = temp;   
+    }
+    public void helper(int[] nums, int ind, List&lt;List&lt;Integer&gt;&gt; res)    
+    {
+        if (ind &gt;= nums.length)
+        { 
+            List&lt;Integer&gt; curr = new ArrayList&lt;&gt;();    
+            for (int i = 0; i &lt; nums.length; i++)    curr.add(nums[i]);    
+            res.add(new ArrayList&lt;&gt;(curr));
+            return;
+        }    
+        for (int i = ind; i &lt; nums.length; i++)    
+        {   
+            swap(nums, i, ind);    
+            helper(nums, ind + 1, res);    
+            swap(nums, i, ind); 
+        }
+    }
+    public List&lt;List&lt;Integer&gt;&gt; permute(int[] nums) {
+        List&lt;List&lt;Integer&gt;&gt; res = new ArrayList&lt;&gt;();
+        helper(nums, 0, res);    
+        return res;    
+    }    </t>
   </si>
   <si>
     <t>https://leetcode.com/problems/n-queens</t>
@@ -366,17 +593,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <sz val="10.000000"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10.000000"/>
-      <color theme="10"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -387,26 +607,43 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11.000000"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.000000"/>
+      <color theme="1"/>
+      <name val="Monaco"/>
+    </font>
+    <font>
       <u/>
-      <sz val="10.000000"/>
+      <color indexed="4"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
       <color indexed="4"/>
       <name val="Arial"/>
     </font>
     <font>
-      <u/>
-      <sz val="10.000000"/>
-      <color rgb="FF1155CC"/>
+      <b/>
+      <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10.000000"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -417,6 +654,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -431,39 +674,52 @@
   </borders>
   <cellStyleXfs count="3">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
+    <xf fontId="1" fillId="2" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
+    <xf fontId="2" fillId="3" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="2" applyFont="1" applyFill="1"/>
+  <cellXfs count="11">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment readingOrder="0"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment readingOrder="0" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="3" borderId="0" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf fontId="7" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf fontId="8" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Good" xfId="2" builtinId="26"/>
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
+    <cellStyle name="Neutral" xfId="2" builtinId="28"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -888,28 +1144,16 @@
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -965,448 +1209,432 @@
     <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.630000000000001" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="81.21875"/>
-    <col customWidth="1" min="2" max="2" width="43.6640625"/>
-    <col customWidth="1" min="3" max="3" width="47.140625"/>
+    <col customWidth="1" min="1" max="1" width="64.140625"/>
+    <col customWidth="1" min="2" max="2" width="94.8515625"/>
+    <col customWidth="1" min="3" max="3" width="176.00390625"/>
   </cols>
   <sheetData>
-    <row r="1" ht="216.75">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="18.600000000000001" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
+    </row>
+    <row r="8" ht="19.199999999999999" customHeight="1">
+      <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" ht="16.800000000000001" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>12</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="19.199999999999999" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1</v>
+      <c r="A12" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1</v>
+      <c r="A13" s="4" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>14</v>
+      <c r="A15" s="4" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>15</v>
+      <c r="A16" s="4" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>16</v>
+      <c r="A17" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" ht="15.75" customHeight="1"/>
+      <c r="A18" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
     <row r="20">
-      <c r="A20" s="4" t="s">
-        <v>18</v>
+      <c r="A20" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="s">
-        <v>19</v>
+      <c r="A21" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="s">
-        <v>20</v>
+      <c r="A23" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="s">
-        <v>21</v>
+      <c r="A24" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="s">
-        <v>22</v>
+      <c r="A25" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="s">
-        <v>23</v>
+      <c r="A26" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="s">
-        <v>24</v>
+      <c r="A27" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="s">
-        <v>25</v>
+      <c r="A28" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="s">
-        <v>26</v>
+      <c r="A29" s="6" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="s">
-        <v>27</v>
+      <c r="A31" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="s">
-        <v>28</v>
+      <c r="A32" s="4" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="s">
-        <v>29</v>
+      <c r="A34" s="7" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="s">
-        <v>30</v>
+      <c r="A35" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="s">
-        <v>31</v>
+      <c r="A36" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="s">
-        <v>32</v>
+      <c r="A37" s="4" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="s">
-        <v>33</v>
+      <c r="A38" s="4" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="s">
-        <v>34</v>
+      <c r="A39" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="s">
-        <v>35</v>
+      <c r="A40" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="s">
-        <v>36</v>
+      <c r="A41" s="4" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="s">
-        <v>37</v>
+      <c r="A43" s="4" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="s">
-        <v>38</v>
+      <c r="A44" s="4" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="s">
-        <v>39</v>
+      <c r="A45" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="s">
-        <v>40</v>
+      <c r="A46" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="s">
-        <v>41</v>
+      <c r="A47" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="s">
-        <v>42</v>
+      <c r="A49" s="4" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="s">
-        <v>43</v>
+      <c r="A50" s="4" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="s">
-        <v>44</v>
+      <c r="A52" s="7" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="s">
-        <v>45</v>
+      <c r="A53" s="4" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="s">
-        <v>46</v>
+      <c r="A54" s="4" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="s">
-        <v>47</v>
+      <c r="A55" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="s">
-        <v>48</v>
+      <c r="A56" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="s">
-        <v>49</v>
+      <c r="A57" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B59" s="7"/>
+      <c r="A59" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B59" s="8"/>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="s">
-        <v>51</v>
+      <c r="A60" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="s">
-        <v>52</v>
+      <c r="A62" s="7" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="s">
-        <v>53</v>
+      <c r="A63" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="6" t="s">
-        <v>54</v>
+      <c r="A65" s="7" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="s">
-        <v>55</v>
+      <c r="A66" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="s">
-        <v>56</v>
+      <c r="A67" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="s">
-        <v>57</v>
+      <c r="A68" s="4" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="s">
-        <v>58</v>
+      <c r="A69" s="4" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="s">
-        <v>59</v>
+      <c r="A70" s="4" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="s">
-        <v>60</v>
+      <c r="A71" s="4" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="7"/>
+      <c r="A72" s="8"/>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="s">
-        <v>61</v>
+      <c r="A73" s="4" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="s">
-        <v>62</v>
+      <c r="A74" s="4" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="s">
-        <v>63</v>
+      <c r="A75" s="4" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="7"/>
+      <c r="A76" s="8"/>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="s">
-        <v>64</v>
+      <c r="A77" s="4" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="7"/>
+      <c r="A78" s="8"/>
     </row>
     <row r="79">
-      <c r="A79" s="7" t="s">
-        <v>65</v>
+      <c r="A79" s="8" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="s">
-        <v>66</v>
+      <c r="A80" s="4" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="s">
-        <v>67</v>
+      <c r="A81" s="4" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="7"/>
+      <c r="A82" s="8"/>
     </row>
     <row r="83">
-      <c r="A83" s="7" t="s">
-        <v>68</v>
+      <c r="A83" s="8" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="s">
-        <v>69</v>
+      <c r="A84" s="4" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="s">
-        <v>70</v>
+      <c r="A85" s="4" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="s">
-        <v>71</v>
+      <c r="A86" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="s">
-        <v>72</v>
+      <c r="A87" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="7"/>
+      <c r="A88" s="8"/>
     </row>
     <row r="89">
-      <c r="A89" s="7" t="s">
-        <v>73</v>
+      <c r="A89" s="8" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="s">
-        <v>74</v>
+      <c r="A90" s="4" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="7"/>
+      <c r="A91" s="8"/>
     </row>
     <row r="92">
-      <c r="A92" s="7"/>
+      <c r="A92" s="8"/>
     </row>
     <row r="93">
-      <c r="A93" s="7"/>
+      <c r="A93" s="8"/>
     </row>
     <row r="95">
-      <c r="A95" s="7"/>
+      <c r="A95" s="8"/>
     </row>
     <row r="96">
-      <c r="A96" s="7"/>
+      <c r="A96" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1478,7 +1706,7 @@
     <hyperlink r:id="rId66" ref="A90"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
@@ -1490,107 +1718,104 @@
     <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.630000000000001" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="66.88671875"/>
+    <col customWidth="1" min="1" max="1" width="66.879999999999995"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+      <c r="A1" s="4" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>76</v>
+      <c r="A2" s="4" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>77</v>
+      <c r="A3" s="4" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="s">
-        <v>78</v>
+      <c r="A5" s="9" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="s">
-        <v>79</v>
+      <c r="A6" s="10" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="s">
-        <v>80</v>
+      <c r="A7" s="10" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="s">
-        <v>81</v>
+      <c r="A8" s="10" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="s">
-        <v>82</v>
+      <c r="A9" s="10" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="s">
-        <v>83</v>
+      <c r="A10" s="10" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="s">
-        <v>84</v>
+      <c r="A11" s="10" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="s">
-        <v>85</v>
+      <c r="A13" s="7" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>86</v>
+      <c r="A14" s="4" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>87</v>
+      <c r="A15" s="4" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>88</v>
+      <c r="A16" s="4" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7"/>
+      <c r="A18" s="8"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="s">
-        <v>89</v>
+      <c r="A19" s="7" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>90</v>
+      <c r="A20" s="4" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="s">
-        <v>91</v>
+      <c r="A21" s="4" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6"/>
+      <c r="A23" s="7"/>
     </row>
     <row r="24">
-      <c r="A24" s="7"/>
+      <c r="A24" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1611,7 +1836,7 @@
     <hyperlink r:id="rId15" ref="A21"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
@@ -1623,114 +1848,114 @@
     <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.630000000000001" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="57.77734375"/>
+    <col customWidth="1" min="1" max="1" width="57.75"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.199999999999999">
-      <c r="A1" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" ht="13.199999999999999">
-      <c r="A2" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="3" ht="13.199999999999999">
-      <c r="A3" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" ht="13.199999999999999">
-      <c r="A4" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" ht="13.199999999999999">
-      <c r="A5" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" ht="13.199999999999999">
-      <c r="A6" s="3" t="s">
-        <v>97</v>
+    <row r="1">
+      <c r="A1" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="10" ht="13.199999999999999">
-      <c r="A10" s="6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" ht="13.199999999999999">
-      <c r="A11" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="12" ht="13.199999999999999">
-      <c r="A12" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" ht="13.199999999999999">
-      <c r="A13" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="14" ht="13.199999999999999">
-      <c r="A14" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="15" ht="13.199999999999999">
-      <c r="A15" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="16" ht="13.199999999999999">
-      <c r="A16" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="17" ht="13.199999999999999">
-      <c r="A17" s="3" t="s">
+    <row r="10">
+      <c r="A10" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="19" ht="13.199999999999999">
-      <c r="A19" s="3" t="s">
+    <row r="12">
+      <c r="A12" s="4" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="20" ht="13.199999999999999">
-      <c r="A20" s="3" t="s">
+    <row r="13">
+      <c r="A13" s="4" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="21" ht="13.199999999999999">
-      <c r="A21" s="3" t="s">
+    <row r="14">
+      <c r="A14" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="22" ht="13.199999999999999">
-      <c r="A22" s="3" t="s">
+    <row r="15">
+      <c r="A15" s="4" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="24" ht="13.199999999999999">
-      <c r="A24" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" ht="13.199999999999999">
-      <c r="A25" s="3" t="s">
+    <row r="16">
+      <c r="A16" s="4" t="s">
         <v>110</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1756,7 +1981,7 @@
     <hyperlink r:id="rId19" ref="A25"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>

--- a/dsa/educosys/DSA Course Questions.xlsx
+++ b/dsa/educosys/DSA Course Questions.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="121">
   <si>
     <t>https://leetcode.com/problems/fibonacci-number</t>
   </si>
@@ -295,7 +295,172 @@
     <t>https://leetcode.com/problems/n-queens</t>
   </si>
   <si>
+    <t xml:space="preserve">* first approach - use recursion to check all possible board configurations, and check for leftUp, left, leftDown paths in the board for checking queens    
+* second approach - maintain three vectors leftUp(2*n - 1), left(n), leftDown(2*n - 1), check for queens if already placed within these three vectors, like leftUp[row + col], left[row], leftDown[(n - 1) + (col - row)].    
+   for a give row, col, if you find any vector has value 1 stored within them, that means you can't place a queen at location row, col.    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /*
+     * recursion with back tracking    
+     * time complexity: O(n! * n) ( first column you have n choices, and second column will have n - 1 choices, third column will have n - 2 choices, fourth column will have n - 3 choices thats n! + and at each step calling isValid() which is taking O(n) )    
+     * space complexity: O(n) + O(n^2) (recursive stack + constructing board)    
+     */
+    // bool isValid(int n, int row, int col, vector&lt;string&gt;&amp; board)
+    // {
+    //     int rowCopy = row, colCopy = col;
+    //     // check for left digonal up    
+    //     while (row &gt;= 0 &amp;&amp; col &gt;= 0)    
+    //     {
+    //         if (board[row][col] == 'Q') return false;
+    //         row--;
+    //         col--;
+    //     }
+    //     // check for left    
+    //     row = rowCopy, col = colCopy;
+    //     while (col &gt;= 0) // O(n)
+    //     {
+    //         if (board[row][col] == 'Q') return false;
+    //         col--;
+    //     }
+    //     // check for left diagonal down    
+    //     row = rowCopy, col = colCopy;    
+    //     while (row &lt;= n - 1 &amp;&amp; col &gt;= 0)    
+    //     {
+    //         if (board[row][col] == 'Q') return false;
+    //         row++;
+    //         col--;    
+    //     }
+    //     return true;    
+    // }
+    // void solve (int n, int col, vector&lt;string&gt;&amp; board, vector&lt;vector&lt;string&gt;&gt;&amp; res)
+    // {
+    //     if (col == n)
+    //     {
+    //         res.push_back(board);
+    //         return;
+    //     }
+    //     for (int row = 0; row &lt; n; row++)    
+    //     {
+    //         if (isValid(n, row, col, board))
+    //         {
+    //             board[row][col] = 'Q';
+    //             solve(n, col + 1, board, res);
+    //             board[row][col] = '.';
+    //         }
+    //     }
+    // }
+    // vector&lt;vector&lt;string&gt;&gt; solveNQueens(int n) {
+    //     vector&lt;vector&lt;string&gt;&gt; res;
+    //     vector&lt;string&gt; board;
+    //     string row(n, '.');
+    //     for (int i = 0; i &lt; n; i++) board.push_back(row);    
+    //     solve(n, 0, board, res);
+    //     return res;
+    // }    
+    /*
+     * recursion with backtracking, but a little optimized    
+     * time complexity: O(n!) ( first column you have n choices, and second column will have n - 1 choices, third column will have n - 2 choices, fourth column will have n - 3 choices thats n!. Here no multiplication of O(n) since we are using leftUp, left, leftDown lists, and checking is O(1))
+     * space complexity: O(n) + O(n^2) + O(n) + O(2 * n - 1) + O(2 * n - 1) ( recursive stack, board, leftUp vector, left vector, leftDown vector ) = O(n) + O(n^2) = O(n + n^2)    
+     */
+    void solve (int n, int col, vector&lt;string&gt;&amp; board, vector&lt;vector&lt;string&gt;&gt;&amp; res, vector&lt;int&gt;&amp; leftUp, vector&lt;int&gt;&amp; left, vector&lt;int&gt;&amp; leftDown)
+    {
+        if (col == n)
+        {
+            res.push_back(board);
+            return;
+        }
+        for (int row = 0; row &lt; n; row++)
+        {
+            if (leftUp[(n - 1) + (col - row)] == 0 &amp;&amp; left[row] == 0 &amp;&amp; leftDown[row + col] == 0)
+            {
+                board[row][col] = 'Q'; 
+                leftUp[(n - 1) + (col - row)] = 1;
+                left[row] = 1;    
+                leftDown[row + col] = 1;    
+                solve(n, col + 1, board, res, leftUp, left, leftDown);
+                board[row][col] = '.';    
+                leftUp[(n - 1) + (col - row)] = 0;
+                left[row] = 0;    
+                leftDown[row + col] = 0;    
+            }
+        }
+    }
+    vector&lt;vector&lt;string&gt;&gt; solveNQueens(int n) {
+        vector&lt;vector&lt;string&gt;&gt; res;
+        vector&lt;string&gt; board;
+        vector&lt;int&gt; leftUp(2 * n - 1, 0), left(n, 0), leftDown(2 * n - 1, 0);
+        string row(n, '.');
+        for (int i = 0; i &lt; n; i++) board.push_back(row);    
+        solve(n, 0, board, res, leftUp, left, leftDown);
+        return res;
+    }</t>
+  </si>
+  <si>
     <t>https://leetcode.com/problems/sudoku-solver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* recursion with back tracking, you only need to solve for one valid solution, so concentrate on where to stop    
+if you find empty cell i.e - '.', check for valid number from 1 to 9    
+if you find a valid number, call recursive call solve again, check for its return value, if it is true, then just return, else back track    
+if you tried all possible values from 1 to 9, still couldn't able to find a valid number, then just return false    
+if you came out of the double for loop, that means sudoku is already solved, just return true    
+* isValid()    
+iterate from index 0 to 8,    
+check row wise board[row][index] == character    
+check column wise board[index][column] == character    
+check 3 * 3 sub matrix board, board[3 * (row/3) + (i/3)][3 * (column/3) + (i % 3)] == character    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /*    
+     * recursion with back tracking    
+     * time complexity: O( 9 ^ k) ( we are checking from 1 to 9 numbers, and there are k empty cells )
+     * space complexity: O(n * n) (recursive stack)    
+     */
+    bool isValid(int row, int col, int c, vector&lt;vector&lt;char&gt;&gt;&amp; board)    
+    {
+        for (int i = 0; i &lt; 9; i++)    
+        {
+            // check row    
+            if (board[row][i] == c) return false;    
+            // check column    
+            if (board[i][col] == c) return false;    
+            // check 3 * 3 sub sudoku matrix    
+            if (board[3 * (row / 3) + (i / 3)][3 * (col / 3) + (i % 3)] == c) return false;    
+        }    
+        return true;    
+    }
+    bool solve(vector&lt;vector&lt;char&gt;&gt;&amp; board)    
+    {
+        for (int i = 0; i &lt; 9; i++)
+        {
+            for (int j = 0; j &lt; 9; j++)    
+            {
+                if (board[i][j] == '.')
+                {
+                    for (char c = '1'; c &lt;= '9'; c++)
+                    {
+                        if (isValid(i, j, c, board))    
+                        {
+                            board[i][j] = c;
+                            if (solve(board) == true)    
+                            {
+                                return true;    
+                            }    
+                            else
+                            {
+                                board[i][j] = '.';    
+                            }
+                        }
+                    }    
+                    return false;    
+                }
+            }
+        }    
+        return true;    
+    }
+    void solveSudoku(vector&lt;vector&lt;char&gt;&gt;&amp; board) {
+        solve(board);
+    }</t>
   </si>
   <si>
     <t>https://leetcode.com/problems/longest-common-subsequence</t>
@@ -1290,250 +1455,262 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="s">
+    <row r="12" ht="19.800000000000001" customHeight="1">
+      <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>19</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" ht="19.199999999999999" customHeight="1">
+      <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B59" s="8"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="72">
@@ -1541,17 +1718,17 @@
     </row>
     <row r="73">
       <c r="A73" s="4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="76">
@@ -1559,7 +1736,7 @@
     </row>
     <row r="77">
       <c r="A77" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="78">
@@ -1567,17 +1744,17 @@
     </row>
     <row r="79">
       <c r="A79" s="8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="82">
@@ -1585,27 +1762,27 @@
     </row>
     <row r="83">
       <c r="A83" s="8" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="88">
@@ -1613,12 +1790,12 @@
     </row>
     <row r="89">
       <c r="A89" s="8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="91">
@@ -1725,72 +1902,72 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18">
@@ -1798,17 +1975,17 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23">
@@ -1855,107 +2032,107 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" ht="16.5" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
